--- a/24-25_KBL_stats.xlsx
+++ b/24-25_KBL_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30013"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\2026\KBL Stats Analyzer 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1391B3-B250-46F7-95EB-D0C30D63459B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62E9FBB-6970-4B24-8D2C-C7F052A9C1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
   </bookViews>
@@ -66,22 +66,13 @@
     <t>평균 득점</t>
   </si>
   <si>
-    <t>FGA</t>
-  </si>
-  <si>
     <t>FG%</t>
-  </si>
-  <si>
-    <t>2PA</t>
   </si>
   <si>
     <t>2P%</t>
   </si>
   <si>
     <t>3P%</t>
-  </si>
-  <si>
-    <t>평균 FT 시도</t>
   </si>
   <si>
     <t>FT%</t>
@@ -1061,19 +1052,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>평균 FG 성공</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>평균 FG 시도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2P</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1109,10 +1092,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>평균 FT 성공</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -1120,6 +1099,30 @@
   </si>
   <si>
     <t>G</t>
+  </si>
+  <si>
+    <t>FGA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2PA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균 FT 시도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균 FT 성공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2086,204 +2089,204 @@
         <v>8</v>
       </c>
       <c r="J1" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="K1" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="L1" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="M1" s="35" t="s">
+        <v>329</v>
+      </c>
+      <c r="N1" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q1" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="K1" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="35" t="s">
+      <c r="R1" s="35" t="s">
+        <v>331</v>
+      </c>
+      <c r="S1" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="U1" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="M1" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="N1" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="38" t="s">
+      <c r="V1" s="35" t="s">
+        <v>336</v>
+      </c>
+      <c r="W1" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="P1" s="38" t="s">
+      <c r="X1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="35" t="s">
-        <v>336</v>
-      </c>
-      <c r="R1" s="35" t="s">
+      <c r="Y1" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="Z1" s="38" t="s">
         <v>337</v>
       </c>
-      <c r="S1" s="35" t="s">
+      <c r="AA1" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="AB1" s="35" t="s">
+        <v>347</v>
+      </c>
+      <c r="AC1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="U1" s="38" t="s">
-        <v>339</v>
-      </c>
-      <c r="V1" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="W1" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="X1" s="35" t="s">
+      <c r="AD1" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="Y1" s="38" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z1" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="AA1" s="35" t="s">
-        <v>344</v>
-      </c>
-      <c r="AB1" s="35" t="s">
+      <c r="AE1" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="AC1" s="35" t="s">
+      <c r="AF1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="AD1" s="38" t="s">
+      <c r="AG1" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="AE1" s="35" t="s">
+      <c r="AH1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="38" t="s">
+      <c r="AI1" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="AG1" s="35" t="s">
+      <c r="AJ1" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="AH1" s="38" t="s">
+      <c r="AK1" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="AI1" s="35" t="s">
+      <c r="AL1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AJ1" s="38" t="s">
+      <c r="AM1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="AK1" s="35" t="s">
+      <c r="AN1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="AL1" s="38" t="s">
+      <c r="AO1" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="AM1" s="35" t="s">
+      <c r="AP1" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="AN1" s="38" t="s">
+      <c r="AQ1" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="AO1" s="35" t="s">
+      <c r="AR1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="AP1" s="38" t="s">
+      <c r="AS1" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="AQ1" s="35" t="s">
+      <c r="AT1" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="AR1" s="38" t="s">
+      <c r="AU1" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="AS1" s="35" t="s">
+      <c r="AV1" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="AT1" s="35" t="s">
+      <c r="AW1" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="AU1" s="35" t="s">
+      <c r="AX1" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="AV1" s="35" t="s">
+      <c r="AY1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="AW1" s="35" t="s">
+      <c r="AZ1" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="AX1" s="35" t="s">
+      <c r="BA1" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="AY1" s="35" t="s">
+      <c r="BB1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="AZ1" s="35" t="s">
+      <c r="BC1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="BA1" s="35" t="s">
+      <c r="BD1" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="BB1" s="35" t="s">
+      <c r="BE1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="BC1" s="35" t="s">
+      <c r="BF1" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="BD1" s="35" t="s">
+      <c r="BG1" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="BE1" s="35" t="s">
+      <c r="BH1" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="BF1" s="35" t="s">
+      <c r="BI1" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="BG1" s="35" t="s">
+      <c r="BJ1" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="BH1" s="35" t="s">
+      <c r="BK1" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="BI1" s="35" t="s">
+      <c r="BL1" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="BJ1" s="35" t="s">
+      <c r="BM1" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="BK1" s="35" t="s">
+      <c r="BN1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="BL1" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="BM1" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="BN1" s="35" t="s">
-        <v>52</v>
-      </c>
       <c r="BO1" s="35" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="BP1" s="35" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="BQ1" s="35" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D2" s="40">
         <v>40</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G2" s="43">
         <v>72360</v>
@@ -2466,24 +2469,24 @@
         <v>14.150398521427748</v>
       </c>
       <c r="BO2" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP2" s="50">
         <v>700000</v>
       </c>
       <c r="BQ2" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A3" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D3" s="52">
         <v>54</v>
@@ -2675,22 +2678,22 @@
         <v>9.5061188811188799</v>
       </c>
       <c r="BO3" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP3" s="50"/>
       <c r="BQ3" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D4" s="54">
         <v>31</v>
@@ -2882,22 +2885,22 @@
         <v>18.433988764044944</v>
       </c>
       <c r="BO4" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP4" s="50"/>
       <c r="BQ4" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A5" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -3089,33 +3092,33 @@
         <v>11.261261261261263</v>
       </c>
       <c r="BO5" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP5" s="50">
         <v>50000</v>
       </c>
       <c r="BQ5" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D6" s="56">
         <v>46</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G6" s="43">
         <v>29854</v>
@@ -3298,24 +3301,24 @@
         <v>8.5266030013642578</v>
       </c>
       <c r="BO6" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP6" s="50">
         <v>85000</v>
       </c>
       <c r="BQ6" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D7" s="57">
         <v>17</v>
@@ -3507,22 +3510,22 @@
         <v>13.399382816306643</v>
       </c>
       <c r="BO7" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP7" s="50"/>
       <c r="BQ7" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D8" s="57">
         <v>34</v>
@@ -3714,24 +3717,24 @@
         <v>6.9541029207232263</v>
       </c>
       <c r="BO8" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP8" s="50">
         <v>100000</v>
       </c>
       <c r="BQ8" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D9" s="55">
         <v>36</v>
@@ -3923,27 +3926,27 @@
         <v>12.087026591458502</v>
       </c>
       <c r="BO9" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP9" s="50">
         <v>130000</v>
       </c>
       <c r="BQ9" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A10" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E10" s="55">
         <v>2</v>
@@ -4132,33 +4135,33 @@
         <v>0</v>
       </c>
       <c r="BO10" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP10" s="50">
         <v>40000</v>
       </c>
       <c r="BQ10" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" s="56">
         <v>45</v>
       </c>
       <c r="E11" s="56" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F11" s="56" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G11" s="43">
         <v>60705</v>
@@ -4341,33 +4344,33 @@
         <v>13.325560089947531</v>
       </c>
       <c r="BO11" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP11" s="50">
         <v>500000</v>
       </c>
       <c r="BQ11" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A12" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D12" s="56">
         <v>1</v>
       </c>
       <c r="E12" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F12" s="56" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G12" s="43">
         <v>89</v>
@@ -4550,31 +4553,31 @@
         <v>0</v>
       </c>
       <c r="BO12" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP12" s="50"/>
       <c r="BQ12" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D13" s="56">
         <v>13</v>
       </c>
       <c r="E13" s="56" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F13" s="56" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G13" s="43">
         <v>4160</v>
@@ -4757,24 +4760,24 @@
         <v>5.5679287305122491</v>
       </c>
       <c r="BO13" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP13" s="50">
         <v>95000</v>
       </c>
       <c r="BQ13" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A14" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D14" s="56">
         <v>1</v>
@@ -4966,33 +4969,33 @@
         <v>0</v>
       </c>
       <c r="BO14" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP14" s="50">
         <v>15629</v>
       </c>
       <c r="BQ14" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D15" s="56">
         <v>41</v>
       </c>
       <c r="E15" s="56" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F15" s="56" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G15" s="43">
         <v>43419</v>
@@ -5175,33 +5178,33 @@
         <v>14.90066225165563</v>
       </c>
       <c r="BO15" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP15" s="50">
         <v>45000</v>
       </c>
       <c r="BQ15" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A16" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D16" s="56">
         <v>14</v>
       </c>
       <c r="E16" s="56" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F16" s="56" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G16" s="43">
         <v>12530</v>
@@ -5384,33 +5387,33 @@
         <v>3.4106412005457027</v>
       </c>
       <c r="BO16" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP16" s="50">
         <v>220000</v>
       </c>
       <c r="BQ16" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A17" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D17" s="56">
         <v>17</v>
       </c>
       <c r="E17" s="56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F17" s="56" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G17" s="43">
         <v>9418</v>
@@ -5593,22 +5596,22 @@
         <v>19.434628975265017</v>
       </c>
       <c r="BO17" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP17" s="50"/>
       <c r="BQ17" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A18" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D18" s="47">
         <v>51</v>
@@ -5800,33 +5803,33 @@
         <v>12.392115698623748</v>
       </c>
       <c r="BO18" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP18" s="50">
         <v>600000</v>
       </c>
       <c r="BQ18" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A19" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D19" s="56">
         <v>47</v>
       </c>
       <c r="E19" s="56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F19" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G19" s="43">
         <v>26461</v>
@@ -6009,33 +6012,33 @@
         <v>21.744382701135539</v>
       </c>
       <c r="BO19" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP19" s="50">
         <v>100000</v>
       </c>
       <c r="BQ19" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A20" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D20" s="56">
         <v>28</v>
       </c>
       <c r="E20" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F20" s="56" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G20" s="43">
         <v>20132</v>
@@ -6218,22 +6221,22 @@
         <v>15.408320493066256</v>
       </c>
       <c r="BO20" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP20" s="50"/>
       <c r="BQ20" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D21" s="59">
         <v>16</v>
@@ -6425,24 +6428,24 @@
         <v>15.033072760072157</v>
       </c>
       <c r="BO21" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP21" s="50">
         <v>175000</v>
       </c>
       <c r="BQ21" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A22" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C22" s="62" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D22" s="22">
         <v>44</v>
@@ -6634,31 +6637,31 @@
         <v>15.271866771977493</v>
       </c>
       <c r="BO22" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP22" s="66"/>
       <c r="BQ22" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D23" s="56">
         <v>11</v>
       </c>
       <c r="E23" s="56" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F23" s="56" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G23" s="43">
         <v>3498</v>
@@ -6841,33 +6844,33 @@
         <v>12.019230769230768</v>
       </c>
       <c r="BO23" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP23" s="50">
         <v>60000</v>
       </c>
       <c r="BQ23" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="24" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D24" s="56">
         <v>5</v>
       </c>
       <c r="E24" s="56" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F24" s="56" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G24" s="43">
         <v>5685</v>
@@ -7050,24 +7053,24 @@
         <v>15.600624024960998</v>
       </c>
       <c r="BO24" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP24" s="50">
         <v>600000</v>
       </c>
       <c r="BQ24" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D25" s="59">
         <v>6</v>
@@ -7259,24 +7262,24 @@
         <v>9.2936802973977706</v>
       </c>
       <c r="BO25" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP25" s="50">
         <v>600000</v>
       </c>
       <c r="BQ25" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A26" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B26" s="61" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C26" s="62" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D26" s="22">
         <v>11</v>
@@ -7468,33 +7471,33 @@
         <v>12.1604729008356</v>
       </c>
       <c r="BO26" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP26" s="50">
         <v>600000</v>
       </c>
       <c r="BQ26" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A27" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D27" s="56">
         <v>3</v>
       </c>
       <c r="E27" s="56" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F27" s="56" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G27" s="43">
         <v>657</v>
@@ -7677,24 +7680,24 @@
         <v>16.666666666666668</v>
       </c>
       <c r="BO27" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP27" s="50">
         <v>16866</v>
       </c>
       <c r="BQ27" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A28" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D28" s="56">
         <v>15</v>
@@ -7886,33 +7889,33 @@
         <v>21.41982864137087</v>
       </c>
       <c r="BO28" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP28" s="50">
         <v>370000</v>
       </c>
       <c r="BQ28" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A29" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D29" s="56">
         <v>19</v>
       </c>
       <c r="E29" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F29" s="56" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G29" s="43">
         <v>27018</v>
@@ -8095,24 +8098,24 @@
         <v>22.164948453608247</v>
       </c>
       <c r="BO29" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP29" s="50">
         <v>370000</v>
       </c>
       <c r="BQ29" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D30" s="59">
         <v>5</v>
@@ -8304,24 +8307,24 @@
         <v>9.0909090909090917</v>
       </c>
       <c r="BO30" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP30" s="50">
         <v>40000</v>
       </c>
       <c r="BQ30" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A31" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B31" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D31" s="56">
         <v>8</v>
@@ -8513,24 +8516,24 @@
         <v>16.666666666666668</v>
       </c>
       <c r="BO31" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP31" s="50">
         <v>165000</v>
       </c>
       <c r="BQ31" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A32" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D32" s="47">
         <v>23</v>
@@ -8722,27 +8725,27 @@
         <v>15.822784810126581</v>
       </c>
       <c r="BO32" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP32" s="50">
         <v>50000</v>
       </c>
       <c r="BQ32" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A33" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B33" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E33" s="56">
         <v>1</v>
@@ -8931,33 +8934,33 @@
         <v>0</v>
       </c>
       <c r="BO33" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP33" s="50">
         <v>50000</v>
       </c>
       <c r="BQ33" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A34" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D34" s="56">
         <v>41</v>
       </c>
       <c r="E34" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F34" s="56" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G34" s="43">
         <v>29110</v>
@@ -9140,33 +9143,33 @@
         <v>14.177693761814746</v>
       </c>
       <c r="BO34" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP34" s="50">
         <v>200000</v>
       </c>
       <c r="BQ34" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A35" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D35" s="56">
         <v>8</v>
       </c>
       <c r="E35" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F35" s="56" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G35" s="43">
         <v>2280</v>
@@ -9349,24 +9352,24 @@
         <v>0</v>
       </c>
       <c r="BO35" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP35" s="50">
         <v>75000</v>
       </c>
       <c r="BQ35" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A36" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>295</v>
+      </c>
+      <c r="C36" s="35" t="s">
         <v>184</v>
-      </c>
-      <c r="B36" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C36" s="35" t="s">
-        <v>187</v>
       </c>
       <c r="D36" s="47">
         <v>35</v>
@@ -9558,25 +9561,25 @@
         <v>18.818760856977416</v>
       </c>
       <c r="BO36" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP36" s="50"/>
       <c r="BQ36" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A37" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E37" s="56">
         <v>3</v>
@@ -9765,24 +9768,24 @@
         <v>25</v>
       </c>
       <c r="BO37" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP37" s="50">
         <v>40000</v>
       </c>
       <c r="BQ37" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D38" s="47">
         <v>36</v>
@@ -9974,33 +9977,33 @@
         <v>7.2648020341445694</v>
       </c>
       <c r="BO38" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP38" s="50">
         <v>80000</v>
       </c>
       <c r="BQ38" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="39" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A39" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D39" s="56">
         <v>19</v>
       </c>
       <c r="E39" s="56" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F39" s="56" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G39" s="43">
         <v>9766</v>
@@ -10183,24 +10186,24 @@
         <v>9.5785440613026829</v>
       </c>
       <c r="BO39" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP39" s="50">
         <v>58000</v>
       </c>
       <c r="BQ39" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="40" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A40" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D40" s="59">
         <v>1</v>
@@ -10392,33 +10395,33 @@
         <v>0</v>
       </c>
       <c r="BO40" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP40" s="50">
         <v>50000</v>
       </c>
       <c r="BQ40" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A41" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D41" s="56">
         <v>54</v>
       </c>
       <c r="E41" s="56" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F41" s="56" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G41" s="43">
         <v>56268</v>
@@ -10601,31 +10604,31 @@
         <v>18.028846153846153</v>
       </c>
       <c r="BO41" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP41" s="50"/>
       <c r="BQ41" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D42" s="56">
         <v>21</v>
       </c>
       <c r="E42" s="56" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F42" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G42" s="43">
         <v>15204</v>
@@ -10808,31 +10811,31 @@
         <v>15.377855887521967</v>
       </c>
       <c r="BO42" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP42" s="50"/>
       <c r="BQ42" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A43" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B43" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D43" s="56">
         <v>14</v>
       </c>
       <c r="E43" s="56" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F43" s="56" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G43" s="43">
         <v>12936</v>
@@ -11015,24 +11018,24 @@
         <v>20.404542228530872</v>
       </c>
       <c r="BO43" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP43" s="50">
         <v>280000</v>
       </c>
       <c r="BQ43" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B44" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D44" s="59">
         <v>27</v>
@@ -11224,31 +11227,31 @@
         <v>11.910838863365662</v>
       </c>
       <c r="BO44" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP44" s="50"/>
       <c r="BQ44" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D45" s="56">
         <v>24</v>
       </c>
       <c r="E45" s="56" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F45" s="56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G45" s="43">
         <v>38112</v>
@@ -11431,22 +11434,22 @@
         <v>11.7455728225515</v>
       </c>
       <c r="BO45" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP45" s="50"/>
       <c r="BQ45" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B46" s="61" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C46" s="73" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D46" s="22">
         <v>51</v>
@@ -11638,31 +11641,31 @@
         <v>11.833066608864879</v>
       </c>
       <c r="BO46" s="50" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="BP46" s="66"/>
       <c r="BQ46" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B47" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D47" s="56">
         <v>54</v>
       </c>
       <c r="E47" s="56" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F47" s="56" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G47" s="43">
         <v>60642</v>
@@ -11845,22 +11848,22 @@
         <v>11.459411503770516</v>
       </c>
       <c r="BO47" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP47" s="50"/>
       <c r="BQ47" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A48" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D48" s="56">
         <v>52</v>
@@ -12052,22 +12055,22 @@
         <v>8.5664714812405123</v>
       </c>
       <c r="BO48" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP48" s="50"/>
       <c r="BQ48" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A49" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D49" s="47">
         <v>2</v>
@@ -12259,24 +12262,24 @@
         <v>0</v>
       </c>
       <c r="BO49" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP49" s="50">
         <v>45000</v>
       </c>
       <c r="BQ49" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A50" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B50" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D50" s="56">
         <v>49</v>
@@ -12468,33 +12471,33 @@
         <v>11.318126414765802</v>
       </c>
       <c r="BO50" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP50" s="50">
         <v>750000</v>
       </c>
       <c r="BQ50" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A51" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B51" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D51" s="56">
         <v>5</v>
       </c>
       <c r="E51" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F51" s="56" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G51" s="43">
         <v>1465</v>
@@ -12677,22 +12680,22 @@
         <v>10.593220338983052</v>
       </c>
       <c r="BO51" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP51" s="50"/>
       <c r="BQ51" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="52" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A52" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B52" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D52" s="56">
         <v>46</v>
@@ -12884,24 +12887,24 @@
         <v>9.4881276761385749</v>
       </c>
       <c r="BO52" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP52" s="50">
         <v>120000</v>
       </c>
       <c r="BQ52" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="53" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D53" s="56">
         <v>47</v>
@@ -13093,31 +13096,31 @@
         <v>12.856150104239054</v>
       </c>
       <c r="BO53" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP53" s="50"/>
       <c r="BQ53" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A54" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B54" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D54" s="56">
         <v>30</v>
       </c>
       <c r="E54" s="56" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F54" s="56" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G54" s="43">
         <v>13590</v>
@@ -13300,24 +13303,24 @@
         <v>15.702108568864963</v>
       </c>
       <c r="BO54" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP54" s="50">
         <v>50000</v>
       </c>
       <c r="BQ54" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A55" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B55" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D55" s="56">
         <v>53</v>
@@ -13509,24 +13512,24 @@
         <v>15.980629539951574</v>
       </c>
       <c r="BO55" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP55" s="50">
         <v>110000</v>
       </c>
       <c r="BQ55" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A56" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B56" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C56" s="53" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D56" s="47">
         <v>9</v>
@@ -13718,33 +13721,33 @@
         <v>8.3333333333333339</v>
       </c>
       <c r="BO56" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP56" s="50">
         <v>45000</v>
       </c>
       <c r="BQ56" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D57" s="56">
         <v>22</v>
       </c>
       <c r="E57" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F57" s="56" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G57" s="43">
         <v>13266</v>
@@ -13927,24 +13930,24 @@
         <v>9.7847358121330714</v>
       </c>
       <c r="BO57" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP57" s="50">
         <v>40000</v>
       </c>
       <c r="BQ57" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="58" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A58" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D58" s="56">
         <v>9</v>
@@ -14136,24 +14139,24 @@
         <v>0</v>
       </c>
       <c r="BO58" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP58" s="50">
         <v>140000</v>
       </c>
       <c r="BQ58" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A59" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B59" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D59" s="56">
         <v>31</v>
@@ -14345,27 +14348,27 @@
         <v>14.270182114705083</v>
       </c>
       <c r="BO59" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP59" s="50">
         <v>41000</v>
       </c>
       <c r="BQ59" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="60" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A60" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B60" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D60" s="56" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E60" s="56">
         <v>10</v>
@@ -14554,33 +14557,33 @@
         <v>23.736055067647754</v>
       </c>
       <c r="BO60" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP60" s="50">
         <v>40000</v>
       </c>
       <c r="BQ60" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="61" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A61" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B61" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D61" s="56">
         <v>40</v>
       </c>
       <c r="E61" s="56" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F61" s="56" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G61" s="43">
         <v>55040</v>
@@ -14763,24 +14766,24 @@
         <v>11.793956394236899</v>
       </c>
       <c r="BO61" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP61" s="50">
         <v>64000</v>
       </c>
       <c r="BQ61" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="62" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A62" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D62" s="59">
         <v>19</v>
@@ -14972,33 +14975,33 @@
         <v>20.016012810248199</v>
       </c>
       <c r="BO62" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP62" s="50">
         <v>137000</v>
       </c>
       <c r="BQ62" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A63" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B63" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D63" s="56">
         <v>38</v>
       </c>
       <c r="E63" s="56" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F63" s="56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G63" s="43">
         <v>19304</v>
@@ -15181,33 +15184,33 @@
         <v>11.1358574610245</v>
       </c>
       <c r="BO63" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP63" s="50">
         <v>64000</v>
       </c>
       <c r="BQ63" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A64" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B64" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D64" s="56">
         <v>28</v>
       </c>
       <c r="E64" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F64" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G64" s="43">
         <v>19124</v>
@@ -15390,24 +15393,24 @@
         <v>16.431924882629108</v>
       </c>
       <c r="BO64" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP64" s="50">
         <v>60000</v>
       </c>
       <c r="BQ64" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A65" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B65" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D65" s="56">
         <v>45</v>
@@ -15599,24 +15602,24 @@
         <v>12.711864406779661</v>
       </c>
       <c r="BO65" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP65" s="50">
         <v>80000</v>
       </c>
       <c r="BQ65" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="66" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A66" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B66" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D66" s="56">
         <v>23</v>
@@ -15808,33 +15811,33 @@
         <v>19.25008369601607</v>
       </c>
       <c r="BO66" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP66" s="50">
         <v>48931</v>
       </c>
       <c r="BQ66" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A67" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D67" s="56">
         <v>46</v>
       </c>
       <c r="E67" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F67" s="56" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G67" s="43">
         <v>31970</v>
@@ -16017,24 +16020,24 @@
         <v>11.748909029875797</v>
       </c>
       <c r="BO67" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP67" s="50">
         <v>550000</v>
       </c>
       <c r="BQ67" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="68" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A68" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B68" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D68" s="59">
         <v>54</v>
@@ -16226,33 +16229,33 @@
         <v>15.026083012020866</v>
       </c>
       <c r="BO68" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP68" s="50">
         <v>220000</v>
       </c>
       <c r="BQ68" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="69" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A69" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B69" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D69" s="56">
         <v>14</v>
       </c>
       <c r="E69" s="56" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F69" s="56" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G69" s="43">
         <v>11396</v>
@@ -16435,22 +16438,22 @@
         <v>12.982195845697328</v>
       </c>
       <c r="BO69" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP69" s="50"/>
       <c r="BQ69" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A70" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B70" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D70" s="59">
         <v>1</v>
@@ -16642,24 +16645,24 @@
         <v>100</v>
       </c>
       <c r="BO70" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP70" s="50">
         <v>45000</v>
       </c>
       <c r="BQ70" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A71" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B71" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D71" s="59">
         <v>40</v>
@@ -16851,33 +16854,33 @@
         <v>11.76355259288305</v>
       </c>
       <c r="BO71" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP71" s="50">
         <v>200000</v>
       </c>
       <c r="BQ71" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A72" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B72" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D72" s="56">
         <v>1</v>
       </c>
       <c r="E72" s="56" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F72" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G72" s="43">
         <v>490</v>
@@ -17060,31 +17063,31 @@
         <v>50</v>
       </c>
       <c r="BO72" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP72" s="50"/>
       <c r="BQ72" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A73" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B73" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D73" s="56">
         <v>3</v>
       </c>
       <c r="E73" s="56" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F73" s="56" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G73" s="43">
         <v>450</v>
@@ -17267,24 +17270,24 @@
         <v>0</v>
       </c>
       <c r="BO73" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP73" s="50">
         <v>55000</v>
       </c>
       <c r="BQ73" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A74" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B74" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D74" s="59">
         <v>24</v>
@@ -17476,33 +17479,33 @@
         <v>19.639934533551553</v>
       </c>
       <c r="BO74" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP74" s="50">
         <v>119772</v>
       </c>
       <c r="BQ74" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A75" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B75" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D75" s="56">
         <v>53</v>
       </c>
       <c r="E75" s="56" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F75" s="56" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G75" s="43">
         <v>94393</v>
@@ -17685,31 +17688,31 @@
         <v>11.252912518534208</v>
       </c>
       <c r="BO75" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP75" s="50"/>
       <c r="BQ75" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A76" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B76" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D76" s="56">
         <v>11</v>
       </c>
       <c r="E76" s="56" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F76" s="56" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G76" s="43">
         <v>3729</v>
@@ -17892,22 +17895,22 @@
         <v>6.25</v>
       </c>
       <c r="BO76" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP76" s="50"/>
       <c r="BQ76" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A77" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B77" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D77" s="56">
         <v>47</v>
@@ -18099,33 +18102,33 @@
         <v>13.384730699218332</v>
       </c>
       <c r="BO77" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP77" s="50">
         <v>310000</v>
       </c>
       <c r="BQ77" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A78" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B78" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D78" s="56">
         <v>52</v>
       </c>
       <c r="E78" s="56" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F78" s="56" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G78" s="43">
         <v>51324</v>
@@ -18308,24 +18311,24 @@
         <v>12.462612163509473</v>
       </c>
       <c r="BO78" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP78" s="50">
         <v>170000</v>
       </c>
       <c r="BQ78" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A79" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B79" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C79" s="53" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D79" s="47">
         <v>6</v>
@@ -18517,24 +18520,24 @@
         <v>0</v>
       </c>
       <c r="BO79" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP79" s="50">
         <v>40000</v>
       </c>
       <c r="BQ79" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A80" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B80" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D80" s="59">
         <v>19</v>
@@ -18726,31 +18729,31 @@
         <v>13.080444735120995</v>
       </c>
       <c r="BO80" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP80" s="50"/>
       <c r="BQ80" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A81" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B81" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D81" s="56">
         <v>7</v>
       </c>
       <c r="E81" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F81" s="56" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G81" s="43">
         <v>2093</v>
@@ -18933,31 +18936,31 @@
         <v>10</v>
       </c>
       <c r="BO81" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP81" s="50"/>
       <c r="BQ81" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A82" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B82" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D82" s="56">
         <v>8</v>
       </c>
       <c r="E82" s="56" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F82" s="56" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G82" s="43">
         <v>9120</v>
@@ -19140,33 +19143,33 @@
         <v>19.247219846022244</v>
       </c>
       <c r="BO82" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP82" s="50">
         <v>560000</v>
       </c>
       <c r="BQ82" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A83" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B83" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D83" s="56">
         <v>3</v>
       </c>
       <c r="E83" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F83" s="56" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G83" s="43">
         <v>843</v>
@@ -19349,24 +19352,24 @@
         <v>25</v>
       </c>
       <c r="BO83" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP83" s="50">
         <v>60000</v>
       </c>
       <c r="BQ83" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A84" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B84" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D84" s="59">
         <v>24</v>
@@ -19558,24 +19561,24 @@
         <v>16.679021497405486</v>
       </c>
       <c r="BO84" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP84" s="50">
         <v>70000</v>
       </c>
       <c r="BQ84" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="85" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A85" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B85" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D85" s="56">
         <v>53</v>
@@ -19767,22 +19770,22 @@
         <v>14.45165512352075</v>
       </c>
       <c r="BO85" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP85" s="50"/>
       <c r="BQ85" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="86" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A86" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B86" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D86" s="56">
         <v>44</v>
@@ -19974,33 +19977,33 @@
         <v>10.162601626016261</v>
       </c>
       <c r="BO86" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP86" s="50">
         <v>78000</v>
       </c>
       <c r="BQ86" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A87" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B87" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D87" s="56">
         <v>52</v>
       </c>
       <c r="E87" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F87" s="56" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G87" s="43">
         <v>73060</v>
@@ -20183,33 +20186,33 @@
         <v>13.7320720170888</v>
       </c>
       <c r="BO87" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP87" s="50">
         <v>170000</v>
       </c>
       <c r="BQ87" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="88" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A88" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B88" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D88" s="56">
         <v>34</v>
       </c>
       <c r="E88" s="56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F88" s="56" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G88" s="43">
         <v>18598</v>
@@ -20392,33 +20395,33 @@
         <v>18.281535648994513</v>
       </c>
       <c r="BO88" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP88" s="50">
         <v>75000</v>
       </c>
       <c r="BQ88" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="89" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A89" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B89" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D89" s="56">
         <v>39</v>
       </c>
       <c r="E89" s="56" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F89" s="56" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G89" s="43">
         <v>63102</v>
@@ -20601,22 +20604,22 @@
         <v>13.930698776660476</v>
       </c>
       <c r="BO89" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP89" s="50"/>
       <c r="BQ89" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="90" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A90" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B90" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C90" s="53" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D90" s="47">
         <v>48</v>
@@ -20808,31 +20811,31 @@
         <v>11.852085967130215</v>
       </c>
       <c r="BO90" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP90" s="50"/>
       <c r="BQ90" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="91" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A91" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B91" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D91" s="56">
         <v>4</v>
       </c>
       <c r="E91" s="56" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F91" s="56" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G91" s="43">
         <v>932</v>
@@ -21015,24 +21018,24 @@
         <v>26.595744680851066</v>
       </c>
       <c r="BO91" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP91" s="50">
         <v>45000</v>
       </c>
       <c r="BQ91" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="92" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A92" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B92" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C92" s="53" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D92" s="47">
         <v>52</v>
@@ -21224,33 +21227,33 @@
         <v>14.882520282372775</v>
       </c>
       <c r="BO92" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP92" s="50">
         <v>500000</v>
       </c>
       <c r="BQ92" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="93" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A93" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B93" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D93" s="56">
         <v>49</v>
       </c>
       <c r="E93" s="56" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F93" s="56" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G93" s="43">
         <v>75117</v>
@@ -21433,31 +21436,31 @@
         <v>7.167308515190415</v>
       </c>
       <c r="BO93" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP93" s="50"/>
       <c r="BQ93" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="94" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A94" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B94" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D94" s="56">
         <v>30</v>
       </c>
       <c r="E94" s="56" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F94" s="56" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G94" s="43">
         <v>49860</v>
@@ -21640,31 +21643,31 @@
         <v>14.652276463440783</v>
       </c>
       <c r="BO94" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP94" s="50"/>
       <c r="BQ94" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="95" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A95" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B95" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D95" s="56">
         <v>37</v>
       </c>
       <c r="E95" s="56" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F95" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G95" s="43">
         <v>18167</v>
@@ -21847,33 +21850,33 @@
         <v>18.564356435643564</v>
       </c>
       <c r="BO95" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP95" s="50">
         <v>67000</v>
       </c>
       <c r="BQ95" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="96" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A96" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B96" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D96" s="56">
         <v>54</v>
       </c>
       <c r="E96" s="56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F96" s="56" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G96" s="43">
         <v>93582</v>
@@ -22056,33 +22059,33 @@
         <v>14.988629315691544</v>
       </c>
       <c r="BO96" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP96" s="50">
         <v>130000</v>
       </c>
       <c r="BQ96" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="97" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A97" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B97" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D97" s="56">
         <v>23</v>
       </c>
       <c r="E97" s="56" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F97" s="56" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G97" s="43">
         <v>12121</v>
@@ -22265,33 +22268,33 @@
         <v>12.942191544434857</v>
       </c>
       <c r="BO97" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP97" s="50">
         <v>45000</v>
       </c>
       <c r="BQ97" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="98" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A98" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B98" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D98" s="56">
         <v>14</v>
       </c>
       <c r="E98" s="56" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F98" s="56" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G98" s="43">
         <v>26572</v>
@@ -22474,22 +22477,22 @@
         <v>11.066843736166444</v>
       </c>
       <c r="BO98" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP98" s="50"/>
       <c r="BQ98" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="99" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A99" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B99" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C99" s="53" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D99" s="47">
         <v>54</v>
@@ -22681,24 +22684,24 @@
         <v>4.2521827871640774</v>
       </c>
       <c r="BO99" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP99" s="50">
         <v>500000</v>
       </c>
       <c r="BQ99" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="100" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A100" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B100" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C100" s="53" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D100" s="47">
         <v>49</v>
@@ -22890,33 +22893,33 @@
         <v>13.531304856641311</v>
       </c>
       <c r="BO100" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP100" s="50">
         <v>310000</v>
       </c>
       <c r="BQ100" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="101" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A101" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B101" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D101" s="56">
         <v>12</v>
       </c>
       <c r="E101" s="56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F101" s="56" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G101" s="43">
         <v>6696</v>
@@ -23099,33 +23102,33 @@
         <v>12.575452716297788</v>
       </c>
       <c r="BO101" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP101" s="50">
         <v>28311</v>
       </c>
       <c r="BQ101" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="102" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A102" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B102" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D102" s="56">
         <v>42</v>
       </c>
       <c r="E102" s="56" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F102" s="56" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G102" s="43">
         <v>76356</v>
@@ -23308,33 +23311,33 @@
         <v>9.7445679217117274</v>
       </c>
       <c r="BO102" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP102" s="50">
         <v>100000</v>
       </c>
       <c r="BQ102" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="103" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A103" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B103" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D103" s="56">
         <v>51</v>
       </c>
       <c r="E103" s="56" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F103" s="56" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G103" s="43">
         <v>49776</v>
@@ -23517,25 +23520,25 @@
         <v>11.973657952504491</v>
       </c>
       <c r="BO103" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP103" s="50"/>
       <c r="BQ103" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="104" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A104" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B104" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D104" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E104" s="56">
         <v>5</v>
@@ -23724,33 +23727,33 @@
         <v>17.152658662092623</v>
       </c>
       <c r="BO104" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP104" s="50">
         <v>70000</v>
       </c>
       <c r="BQ104" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="105" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A105" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B105" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D105" s="56">
         <v>1</v>
       </c>
       <c r="E105" s="56" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F105" s="56" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G105" s="43">
         <v>334</v>
@@ -23933,33 +23936,33 @@
         <v>0</v>
       </c>
       <c r="BO105" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP105" s="50">
         <v>40000</v>
       </c>
       <c r="BQ105" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="106" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A106" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B106" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D106" s="56">
         <v>36</v>
       </c>
       <c r="E106" s="56" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F106" s="56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G106" s="43">
         <v>16272</v>
@@ -24142,33 +24145,33 @@
         <v>20.257826887661142</v>
       </c>
       <c r="BO106" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP106" s="50">
         <v>50000</v>
       </c>
       <c r="BQ106" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="107" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A107" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B107" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D107" s="56">
         <v>42</v>
       </c>
       <c r="E107" s="56" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F107" s="56" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G107" s="43">
         <v>55188</v>
@@ -24351,33 +24354,33 @@
         <v>12.144013715591962</v>
       </c>
       <c r="BO107" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP107" s="50">
         <v>300000</v>
       </c>
       <c r="BQ107" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="108" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A108" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B108" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D108" s="56">
         <v>30</v>
       </c>
       <c r="E108" s="56" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F108" s="56" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G108" s="43">
         <v>34560</v>
@@ -24560,31 +24563,31 @@
         <v>9.3594009983361062</v>
       </c>
       <c r="BO108" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP108" s="50"/>
       <c r="BQ108" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="109" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A109" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B109" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D109" s="56">
         <v>52</v>
       </c>
       <c r="E109" s="56" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F109" s="56" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G109" s="43">
         <v>45968</v>
@@ -24767,24 +24770,24 @@
         <v>9.0097820490818599</v>
       </c>
       <c r="BO109" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP109" s="50">
         <v>90000</v>
       </c>
       <c r="BQ109" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="110" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A110" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B110" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D110" s="56">
         <v>1</v>
@@ -24976,22 +24979,22 @@
         <v>0</v>
       </c>
       <c r="BO110" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP110" s="50"/>
       <c r="BQ110" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="111" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A111" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B111" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C111" s="25" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D111" s="56">
         <v>16</v>
@@ -25183,33 +25186,33 @@
         <v>11.928429423459246</v>
       </c>
       <c r="BO111" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP111" s="50">
         <v>430000</v>
       </c>
       <c r="BQ111" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="112" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A112" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B112" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C112" s="25" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D112" s="56">
         <v>28</v>
       </c>
       <c r="E112" s="56" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F112" s="56" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G112" s="43">
         <v>37156</v>
@@ -25392,24 +25395,24 @@
         <v>12.427506213753107</v>
       </c>
       <c r="BO112" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP112" s="50">
         <v>430000</v>
       </c>
       <c r="BQ112" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="113" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A113" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B113" s="61" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C113" s="62" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D113" s="22">
         <v>44</v>
@@ -25601,33 +25604,33 @@
         <v>12.246023744555339</v>
       </c>
       <c r="BO113" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP113" s="50">
         <v>430000</v>
       </c>
       <c r="BQ113" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="114" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A114" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B114" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D114" s="56">
         <v>5</v>
       </c>
       <c r="E114" s="56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F114" s="56" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G114" s="43">
         <v>595</v>
@@ -25810,27 +25813,27 @@
         <v>0</v>
       </c>
       <c r="BO114" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP114" s="50">
         <v>48000</v>
       </c>
       <c r="BQ114" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="115" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A115" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B115" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D115" s="56" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E115" s="56">
         <v>8</v>
@@ -26019,24 +26022,24 @@
         <v>40</v>
       </c>
       <c r="BO115" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP115" s="50">
         <v>270000</v>
       </c>
       <c r="BQ115" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="116" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A116" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B116" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D116" s="56">
         <v>21</v>
@@ -26228,33 +26231,33 @@
         <v>11.904761904761905</v>
       </c>
       <c r="BO116" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP116" s="50">
         <v>75000</v>
       </c>
       <c r="BQ116" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="117" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A117" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B117" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D117" s="56">
         <v>54</v>
       </c>
       <c r="E117" s="56" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F117" s="56" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G117" s="43">
         <v>108378</v>
@@ -26437,22 +26440,22 @@
         <v>13.005554251740593</v>
       </c>
       <c r="BO117" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP117" s="50"/>
       <c r="BQ117" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="118" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A118" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B118" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D118" s="56">
         <v>24</v>
@@ -26644,33 +26647,33 @@
         <v>14.101531023368251</v>
       </c>
       <c r="BO118" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP118" s="50">
         <v>65000</v>
       </c>
       <c r="BQ118" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="119" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A119" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B119" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D119" s="56">
         <v>54</v>
       </c>
       <c r="E119" s="56" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F119" s="56" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G119" s="43">
         <v>95256</v>
@@ -26853,33 +26856,33 @@
         <v>10.548523206751055</v>
       </c>
       <c r="BO119" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP119" s="50">
         <v>500000</v>
       </c>
       <c r="BQ119" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="120" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A120" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B120" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D120" s="56">
         <v>2</v>
       </c>
       <c r="E120" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F120" s="56" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G120" s="43">
         <v>598</v>
@@ -27062,33 +27065,33 @@
         <v>0</v>
       </c>
       <c r="BO120" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP120" s="50">
         <v>40000</v>
       </c>
       <c r="BQ120" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="121" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A121" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B121" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D121" s="56">
         <v>33</v>
       </c>
       <c r="E121" s="56" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F121" s="56" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G121" s="43">
         <v>25740</v>
@@ -27271,24 +27274,24 @@
         <v>8.7229588276343328</v>
       </c>
       <c r="BO121" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP121" s="50">
         <v>54000</v>
       </c>
       <c r="BQ121" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="122" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A122" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B122" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D122" s="56">
         <v>54</v>
@@ -27480,24 +27483,24 @@
         <v>12.962858592120837</v>
       </c>
       <c r="BO122" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP122" s="50">
         <v>290000</v>
       </c>
       <c r="BQ122" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="123" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A123" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B123" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D123" s="59">
         <v>9</v>
@@ -27689,24 +27692,24 @@
         <v>15.527950310559005</v>
       </c>
       <c r="BO123" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP123" s="50">
         <v>50000</v>
       </c>
       <c r="BQ123" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="124" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A124" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B124" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D124" s="59">
         <v>6</v>
@@ -27898,27 +27901,27 @@
         <v>14.285714285714286</v>
       </c>
       <c r="BO124" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP124" s="50">
         <v>70000</v>
       </c>
       <c r="BQ124" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="125" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A125" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B125" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D125" s="56" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E125" s="56">
         <v>11</v>
@@ -28107,24 +28110,24 @@
         <v>14.519986334130509</v>
       </c>
       <c r="BO125" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP125" s="50">
         <v>70000</v>
       </c>
       <c r="BQ125" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="126" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A126" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B126" s="61" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C126" s="62" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D126" s="22">
         <v>43</v>
@@ -28316,27 +28319,27 @@
         <v>14.487297211095687</v>
       </c>
       <c r="BO126" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP126" s="50">
         <v>70000</v>
       </c>
       <c r="BQ126" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="127" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A127" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B127" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D127" s="59" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E127" s="60">
         <v>23</v>
@@ -28525,24 +28528,24 @@
         <v>10.350379513915509</v>
       </c>
       <c r="BO127" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP127" s="50">
         <v>150000</v>
       </c>
       <c r="BQ127" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="128" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A128" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B128" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D128" s="56">
         <v>8</v>
@@ -28734,33 +28737,33 @@
         <v>0</v>
       </c>
       <c r="BO128" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP128" s="50">
         <v>45000</v>
       </c>
       <c r="BQ128" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="129" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A129" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B129" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D129" s="56">
         <v>1</v>
       </c>
       <c r="E129" s="56" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F129" s="56" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G129" s="43">
         <v>838</v>
@@ -28943,33 +28946,33 @@
         <v>50</v>
       </c>
       <c r="BO129" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP129" s="50">
         <v>48000</v>
       </c>
       <c r="BQ129" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="130" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A130" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B130" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D130" s="56">
         <v>54</v>
       </c>
       <c r="E130" s="56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F130" s="56" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G130" s="43">
         <v>93312</v>
@@ -29152,27 +29155,27 @@
         <v>14.640431014289062</v>
       </c>
       <c r="BO130" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP130" s="50">
         <v>550000</v>
       </c>
       <c r="BQ130" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="131" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A131" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B131" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D131" s="59" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E131" s="60">
         <v>29</v>
@@ -29361,33 +29364,33 @@
         <v>20.452613684657884</v>
       </c>
       <c r="BO131" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP131" s="50">
         <v>360000</v>
       </c>
       <c r="BQ131" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="132" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A132" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B132" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D132" s="56">
         <v>32</v>
       </c>
       <c r="E132" s="56" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F132" s="56" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G132" s="43">
         <v>59936</v>
@@ -29570,24 +29573,24 @@
         <v>11.894090877749431</v>
       </c>
       <c r="BO132" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP132" s="50">
         <v>500000</v>
       </c>
       <c r="BQ132" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="133" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A133" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B133" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D133" s="59">
         <v>31</v>
@@ -29779,33 +29782,33 @@
         <v>20.378219758721876</v>
       </c>
       <c r="BO133" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP133" s="50">
         <v>250000</v>
       </c>
       <c r="BQ133" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="134" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A134" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B134" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D134" s="56">
         <v>30</v>
       </c>
       <c r="E134" s="56" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F134" s="56" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G134" s="43">
         <v>13830</v>
@@ -29988,33 +29991,33 @@
         <v>17.361111111111111</v>
       </c>
       <c r="BO134" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP134" s="50">
         <v>60000</v>
       </c>
       <c r="BQ134" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="135" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A135" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B135" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D135" s="56">
         <v>7</v>
       </c>
       <c r="E135" s="56" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F135" s="56" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G135" s="43">
         <v>1393</v>
@@ -30197,22 +30200,22 @@
         <v>10.593220338983052</v>
       </c>
       <c r="BO135" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP135" s="50"/>
       <c r="BQ135" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="136" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A136" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B136" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D136" s="56">
         <v>37</v>
@@ -30404,24 +30407,24 @@
         <v>13.440860215053764</v>
       </c>
       <c r="BO136" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP136" s="50">
         <v>90000</v>
       </c>
       <c r="BQ136" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="137" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A137" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B137" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D137" s="56">
         <v>5</v>
@@ -30613,33 +30616,33 @@
         <v>0</v>
       </c>
       <c r="BO137" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP137" s="50">
         <v>40000</v>
       </c>
       <c r="BQ137" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="138" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A138" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B138" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D138" s="56">
         <v>54</v>
       </c>
       <c r="E138" s="56" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F138" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G138" s="43">
         <v>68580</v>
@@ -30822,33 +30825,33 @@
         <v>18.161497625034926</v>
       </c>
       <c r="BO138" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP138" s="50">
         <v>240000</v>
       </c>
       <c r="BQ138" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="139" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A139" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B139" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D139" s="56">
         <v>52</v>
       </c>
       <c r="E139" s="56" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F139" s="56" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G139" s="43">
         <v>63440</v>
@@ -31031,24 +31034,24 @@
         <v>8.9596003475238923</v>
       </c>
       <c r="BO139" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP139" s="50">
         <v>150000</v>
       </c>
       <c r="BQ139" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="140" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A140" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B140" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D140" s="56">
         <v>9</v>
@@ -31240,22 +31243,22 @@
         <v>0</v>
       </c>
       <c r="BO140" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP140" s="50"/>
       <c r="BQ140" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="141" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A141" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B141" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D141" s="56">
         <v>2</v>
@@ -31447,22 +31450,22 @@
         <v>8.4175084175084169</v>
       </c>
       <c r="BO141" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP141" s="50"/>
       <c r="BQ141" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="142" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A142" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B142" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C142" s="53" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D142" s="47">
         <v>54</v>
@@ -31654,22 +31657,22 @@
         <v>8.3467387015509757</v>
       </c>
       <c r="BO142" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP142" s="50"/>
       <c r="BQ142" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="143" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A143" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B143" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C143" s="75" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D143" s="47">
         <v>23</v>
@@ -31861,24 +31864,24 @@
         <v>0</v>
       </c>
       <c r="BO143" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP143" s="50">
         <v>70000</v>
       </c>
       <c r="BQ143" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="144" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A144" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B144" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D144" s="56">
         <v>38</v>
@@ -32070,24 +32073,24 @@
         <v>4.7326076668244204</v>
       </c>
       <c r="BO144" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP144" s="50">
         <v>250000</v>
       </c>
       <c r="BQ144" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="145" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A145" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D145" s="56">
         <v>50</v>
@@ -32279,24 +32282,24 @@
         <v>15.979302998021609</v>
       </c>
       <c r="BO145" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP145" s="50">
         <v>350000</v>
       </c>
       <c r="BQ145" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A146" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B146" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D146" s="56">
         <v>3</v>
@@ -32305,7 +32308,7 @@
         <v>3</v>
       </c>
       <c r="F146" s="56" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G146" s="43">
         <v>540</v>
@@ -32488,27 +32491,27 @@
         <v>0</v>
       </c>
       <c r="BO146" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP146" s="50">
         <v>40000</v>
       </c>
       <c r="BQ146" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A147" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B147" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D147" s="59" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E147" s="60">
         <v>24</v>
@@ -32697,22 +32700,22 @@
         <v>15.036231884057971</v>
       </c>
       <c r="BO147" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP147" s="50"/>
       <c r="BQ147" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A148" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B148" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D148" s="56">
         <v>37</v>
@@ -32904,24 +32907,24 @@
         <v>9.1936801961318437</v>
       </c>
       <c r="BO148" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP148" s="50">
         <v>550000</v>
       </c>
       <c r="BQ148" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="149" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A149" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C149" s="53" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D149" s="47">
         <v>2</v>
@@ -33113,33 +33116,33 @@
         <v>50</v>
       </c>
       <c r="BO149" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP149" s="50">
         <v>45000</v>
       </c>
       <c r="BQ149" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="150" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A150" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D150" s="56">
         <v>40</v>
       </c>
       <c r="E150" s="56" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F150" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G150" s="43">
         <v>38560</v>
@@ -33322,33 +33325,33 @@
         <v>11.361484567316795</v>
       </c>
       <c r="BO150" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP150" s="50">
         <v>80000</v>
       </c>
       <c r="BQ150" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="151" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A151" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D151" s="56">
         <v>1</v>
       </c>
       <c r="E151" s="56" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F151" s="56" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G151" s="43">
         <v>164</v>
@@ -33531,33 +33534,33 @@
         <v>0</v>
       </c>
       <c r="BO151" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP151" s="50">
         <v>45000</v>
       </c>
       <c r="BQ151" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="152" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A152" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D152" s="56">
         <v>19</v>
       </c>
       <c r="E152" s="56" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F152" s="56" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G152" s="43">
         <v>23180</v>
@@ -33740,33 +33743,33 @@
         <v>10.641316685584565</v>
       </c>
       <c r="BO152" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP152" s="50">
         <v>57580</v>
       </c>
       <c r="BQ152" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="153" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A153" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D153" s="56">
         <v>52</v>
       </c>
       <c r="E153" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F153" s="56" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G153" s="43">
         <v>71916</v>
@@ -33949,33 +33952,33 @@
         <v>18.871773946750995</v>
       </c>
       <c r="BO153" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP153" s="50">
         <v>450000</v>
       </c>
       <c r="BQ153" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="154" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A154" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D154" s="56">
         <v>18</v>
       </c>
       <c r="E154" s="56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F154" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G154" s="43">
         <v>9900</v>
@@ -34158,31 +34161,31 @@
         <v>16.94473409801877</v>
       </c>
       <c r="BO154" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP154" s="50"/>
       <c r="BQ154" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="155" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A155" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D155" s="56">
         <v>54</v>
       </c>
       <c r="E155" s="56" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F155" s="56" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G155" s="43">
         <v>86238</v>
@@ -34365,24 +34368,24 @@
         <v>10.464114243506094</v>
       </c>
       <c r="BO155" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP155" s="50">
         <v>110000</v>
       </c>
       <c r="BQ155" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="156" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A156" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D156" s="59">
         <v>30</v>
@@ -34574,33 +34577,33 @@
         <v>11.165245635403979</v>
       </c>
       <c r="BO156" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP156" s="50">
         <v>90000</v>
       </c>
       <c r="BQ156" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="157" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A157" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D157" s="56">
         <v>49</v>
       </c>
       <c r="E157" s="56" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F157" s="56" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G157" s="43">
         <v>53655</v>
@@ -34783,33 +34786,33 @@
         <v>13.189629182996683</v>
       </c>
       <c r="BO157" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP157" s="50">
         <v>150000</v>
       </c>
       <c r="BQ157" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="158" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A158" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D158" s="56">
         <v>7</v>
       </c>
       <c r="E158" s="56" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F158" s="56" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G158" s="43">
         <v>4893</v>
@@ -34992,31 +34995,31 @@
         <v>14.595496246872393</v>
       </c>
       <c r="BO158" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP158" s="50"/>
       <c r="BQ158" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="159" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A159" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D159" s="56">
         <v>23</v>
       </c>
       <c r="E159" s="56" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F159" s="56" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G159" s="43">
         <v>32752</v>
@@ -35199,24 +35202,24 @@
         <v>13.243863676496556</v>
       </c>
       <c r="BO159" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP159" s="50">
         <v>420000</v>
       </c>
       <c r="BQ159" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="160" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A160" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C160" s="25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D160" s="59">
         <v>29</v>
@@ -35408,24 +35411,24 @@
         <v>14.048890137679122</v>
       </c>
       <c r="BO160" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP160" s="50">
         <v>420000</v>
       </c>
       <c r="BQ160" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="161" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A161" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B161" s="61" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C161" s="73" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D161" s="22">
         <v>52</v>
@@ -35617,33 +35620,33 @@
         <v>13.692820741386832</v>
       </c>
       <c r="BO161" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP161" s="50">
         <v>420000</v>
       </c>
       <c r="BQ161" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="162" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A162" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D162" s="56">
         <v>43</v>
       </c>
       <c r="E162" s="56" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F162" s="56" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G162" s="43">
         <v>50353</v>
@@ -35826,24 +35829,24 @@
         <v>10.285949393128986</v>
       </c>
       <c r="BO162" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP162" s="50">
         <v>350000</v>
       </c>
       <c r="BQ162" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="163" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A163" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D163" s="59">
         <v>23</v>
@@ -36035,22 +36038,22 @@
         <v>11.409736308316431</v>
       </c>
       <c r="BO163" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP163" s="50"/>
       <c r="BQ163" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="164" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A164" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B164" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D164" s="56">
         <v>4</v>
@@ -36242,31 +36245,31 @@
         <v>12.330456226880395</v>
       </c>
       <c r="BO164" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP164" s="50"/>
       <c r="BQ164" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="165" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A165" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B165" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D165" s="56">
         <v>1</v>
       </c>
       <c r="E165" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F165" s="56" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G165" s="43">
         <v>257</v>
@@ -36449,24 +36452,24 @@
         <v>0</v>
       </c>
       <c r="BO165" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP165" s="50">
         <v>50000</v>
       </c>
       <c r="BQ165" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="166" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A166" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B166" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D166" s="56">
         <v>28</v>
@@ -36658,31 +36661,31 @@
         <v>16.462841015992474</v>
       </c>
       <c r="BO166" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP166" s="50"/>
       <c r="BQ166" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="167" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A167" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B167" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D167" s="56">
         <v>19</v>
       </c>
       <c r="E167" s="56" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F167" s="56" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G167" s="43">
         <v>7201</v>
@@ -36865,27 +36868,27 @@
         <v>12.69035532994924</v>
       </c>
       <c r="BO167" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP167" s="50">
         <v>45000</v>
       </c>
       <c r="BQ167" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="168" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A168" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B168" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D168" s="56" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E168" s="56">
         <v>2</v>
@@ -37074,24 +37077,24 @@
         <v>0</v>
       </c>
       <c r="BO168" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP168" s="50">
         <v>85000</v>
       </c>
       <c r="BQ168" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="169" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A169" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B169" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D169" s="56">
         <v>2</v>
@@ -37283,24 +37286,24 @@
         <v>0</v>
       </c>
       <c r="BO169" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP169" s="50">
         <v>40833</v>
       </c>
       <c r="BQ169" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="170" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A170" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B170" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D170" s="56">
         <v>1</v>
@@ -37492,25 +37495,25 @@
         <v>0</v>
       </c>
       <c r="BO170" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP170" s="50"/>
       <c r="BQ170" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="171" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A171" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B171" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D171" s="56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E171" s="56">
         <v>10</v>
@@ -37699,33 +37702,33 @@
         <v>14.998125234345705</v>
       </c>
       <c r="BO171" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP171" s="50">
         <v>70000</v>
       </c>
       <c r="BQ171" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="172" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A172" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B172" s="35" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D172" s="56">
         <v>33</v>
       </c>
       <c r="E172" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F172" s="56" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G172" s="43">
         <v>21582</v>
@@ -37908,24 +37911,24 @@
         <v>15.933715742511154</v>
       </c>
       <c r="BO172" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP172" s="50">
         <v>270000</v>
       </c>
       <c r="BQ172" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="173" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A173" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B173" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C173" s="53" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D173" s="47">
         <v>46</v>
@@ -38117,27 +38120,27 @@
         <v>12.790240062967335</v>
       </c>
       <c r="BO173" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP173" s="50">
         <v>300000</v>
       </c>
       <c r="BQ173" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="174" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A174" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B174" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D174" s="59" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E174" s="60">
         <v>28</v>
@@ -38326,33 +38329,33 @@
         <v>16.485144847003038</v>
       </c>
       <c r="BO174" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP174" s="50">
         <v>210000</v>
       </c>
       <c r="BQ174" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="175" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A175" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B175" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C175" s="25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D175" s="56">
         <v>18</v>
       </c>
       <c r="E175" s="56" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F175" s="56" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G175" s="43">
         <v>22536</v>
@@ -38535,24 +38538,24 @@
         <v>18.879173290937995</v>
       </c>
       <c r="BO175" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP175" s="50">
         <v>400000</v>
       </c>
       <c r="BQ175" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="176" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A176" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B176" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D176" s="59">
         <v>34</v>
@@ -38744,24 +38747,24 @@
         <v>13.822688274547186</v>
       </c>
       <c r="BO176" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP176" s="50">
         <v>400000</v>
       </c>
       <c r="BQ176" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="177" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A177" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B177" s="61" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C177" s="73" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D177" s="22">
         <v>52</v>
@@ -38953,24 +38956,24 @@
         <v>15.573010010990156</v>
       </c>
       <c r="BO177" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP177" s="50">
         <v>400000</v>
       </c>
       <c r="BQ177" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="178" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A178" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B178" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D178" s="56">
         <v>1</v>
@@ -39162,24 +39165,24 @@
         <v>34.722222222222221</v>
       </c>
       <c r="BO178" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP178" s="50">
         <v>45000</v>
       </c>
       <c r="BQ178" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="179" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A179" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B179" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D179" s="56">
         <v>45</v>
@@ -39371,24 +39374,24 @@
         <v>9.0375056484410301</v>
       </c>
       <c r="BO179" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP179" s="50">
         <v>400000</v>
       </c>
       <c r="BQ179" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="180" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A180" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B180" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D180" s="56">
         <v>52</v>
@@ -39580,24 +39583,24 @@
         <v>9.9800399201596814</v>
       </c>
       <c r="BO180" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP180" s="50">
         <v>130000</v>
       </c>
       <c r="BQ180" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="181" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A181" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B181" s="35" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C181" s="53" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D181" s="47">
         <v>31</v>
@@ -39789,33 +39792,33 @@
         <v>24.770869457517957</v>
       </c>
       <c r="BO181" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP181" s="50">
         <v>220000</v>
       </c>
       <c r="BQ181" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="182" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A182" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B182" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D182" s="56">
         <v>17</v>
       </c>
       <c r="E182" s="56" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F182" s="56" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G182" s="43">
         <v>27897</v>
@@ -39998,24 +40001,24 @@
         <v>13.490485657483669</v>
       </c>
       <c r="BO182" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP182" s="50">
         <v>600000</v>
       </c>
       <c r="BQ182" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="183" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A183" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B183" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D183" s="56">
         <v>23</v>
@@ -40207,33 +40210,33 @@
         <v>20.080321285140563</v>
       </c>
       <c r="BO183" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP183" s="50">
         <v>50000</v>
       </c>
       <c r="BQ183" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="184" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A184" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B184" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D184" s="56">
         <v>22</v>
       </c>
       <c r="E184" s="56" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F184" s="56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G184" s="43">
         <v>11264</v>
@@ -40416,24 +40419,24 @@
         <v>10.295126973232669</v>
       </c>
       <c r="BO184" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP184" s="50">
         <v>250000</v>
       </c>
       <c r="BQ184" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="185" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A185" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B185" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C185" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D185" s="77">
         <v>27</v>
@@ -40625,27 +40628,27 @@
         <v>23.328149300155523</v>
       </c>
       <c r="BO185" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP185" s="50">
         <v>62000</v>
       </c>
       <c r="BQ185" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="186" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A186" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B186" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D186" s="57" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E186" s="58">
         <v>18</v>
@@ -40834,33 +40837,33 @@
         <v>9.7821833833311587</v>
       </c>
       <c r="BO186" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP186" s="50">
         <v>250000</v>
       </c>
       <c r="BQ186" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="187" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A187" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B187" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D187" s="55">
         <v>25</v>
       </c>
       <c r="E187" s="55" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F187" s="55" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G187" s="43">
         <v>14050</v>
@@ -41043,31 +41046,31 @@
         <v>6.8073519400953035</v>
       </c>
       <c r="BO187" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP187" s="50"/>
       <c r="BQ187" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="188" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A188" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B188" s="35" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D188" s="55">
         <v>48</v>
       </c>
       <c r="E188" s="55" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F188" s="55" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G188" s="43">
         <v>68832</v>
@@ -41250,31 +41253,31 @@
         <v>18.236429950654365</v>
       </c>
       <c r="BO188" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP188" s="50"/>
       <c r="BQ188" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="189" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A189" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B189" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D189" s="55">
         <v>50</v>
       </c>
       <c r="E189" s="55" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F189" s="55" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G189" s="43">
         <v>78950</v>
@@ -41457,22 +41460,22 @@
         <v>10.213741218673707</v>
       </c>
       <c r="BO189" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP189" s="50"/>
       <c r="BQ189" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="190" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A190" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B190" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C190" s="78" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D190" s="57">
         <v>27</v>
@@ -41664,31 +41667,31 @@
         <v>13.894502829426031</v>
       </c>
       <c r="BO190" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP190" s="50"/>
       <c r="BQ190" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A191" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B191" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D191" s="55">
         <v>27</v>
       </c>
       <c r="E191" s="55" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F191" s="55" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G191" s="43">
         <v>47439</v>
@@ -41871,22 +41874,22 @@
         <v>11.183407889385929</v>
       </c>
       <c r="BO191" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP191" s="50"/>
       <c r="BQ191" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="192" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A192" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B192" s="61" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C192" s="73" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D192" s="22">
         <v>54</v>
@@ -42078,31 +42081,31 @@
         <v>12.538955359405982</v>
       </c>
       <c r="BO192" s="50" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="BP192" s="66"/>
       <c r="BQ192" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="193" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A193" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B193" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D193" s="55">
         <v>52</v>
       </c>
       <c r="E193" s="55" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F193" s="55" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G193" s="43">
         <v>45188</v>
@@ -42285,31 +42288,31 @@
         <v>18.648984666390387</v>
       </c>
       <c r="BO193" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP193" s="50"/>
       <c r="BQ193" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="194" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A194" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B194" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D194" s="55">
         <v>23</v>
       </c>
       <c r="E194" s="55" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F194" s="55" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G194" s="43">
         <v>43447</v>
@@ -42492,22 +42495,22 @@
         <v>14.482758620689655</v>
       </c>
       <c r="BO194" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="BP194" s="50"/>
       <c r="BQ194" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="195" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A195" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B195" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D195" s="57">
         <v>35</v>
@@ -42699,22 +42702,22 @@
         <v>13.712942405641897</v>
       </c>
       <c r="BO195" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP195" s="50"/>
       <c r="BQ195" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="196" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A196" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B196" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C196" s="53" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D196" s="57">
         <v>51</v>
@@ -42906,22 +42909,22 @@
         <v>10.871816110996066</v>
       </c>
       <c r="BO196" s="50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BP196" s="50"/>
       <c r="BQ196" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="197" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A197" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B197" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D197" s="55">
         <v>42</v>
@@ -43113,33 +43116,33 @@
         <v>11.051759071652238</v>
       </c>
       <c r="BO197" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP197" s="50">
         <v>340000</v>
       </c>
       <c r="BQ197" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="198" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A198" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B198" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D198" s="55">
         <v>19</v>
       </c>
       <c r="E198" s="55" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F198" s="55" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G198" s="43">
         <v>7942</v>
@@ -43322,24 +43325,24 @@
         <v>22.977941176470587</v>
       </c>
       <c r="BO198" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP198" s="50">
         <v>75000</v>
       </c>
       <c r="BQ198" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="199" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A199" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B199" s="35" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C199" s="53" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D199" s="57">
         <v>44</v>
@@ -43531,24 +43534,24 @@
         <v>9.6631695196024303</v>
       </c>
       <c r="BO199" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP199" s="50">
         <v>35387</v>
       </c>
       <c r="BQ199" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="200" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A200" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B200" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D200" s="55">
         <v>52</v>
@@ -43740,24 +43743,24 @@
         <v>18.263323924954342</v>
       </c>
       <c r="BO200" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP200" s="50">
         <v>150000</v>
       </c>
       <c r="BQ200" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="201" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A201" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B201" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D201" s="55">
         <v>44</v>
@@ -43949,33 +43952,33 @@
         <v>8.2855321861057991</v>
       </c>
       <c r="BO201" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP201" s="50">
         <v>360000</v>
       </c>
       <c r="BQ201" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="202" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A202" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B202" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D202" s="55">
         <v>9</v>
       </c>
       <c r="E202" s="55" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F202" s="55" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G202" s="43">
         <v>3375</v>
@@ -44158,24 +44161,24 @@
         <v>20.949720670391063</v>
       </c>
       <c r="BO202" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP202" s="50">
         <v>80000</v>
       </c>
       <c r="BQ202" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="203" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A203" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B203" s="35" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D203" s="55">
         <v>37</v>
@@ -44367,33 +44370,33 @@
         <v>14.338731443994602</v>
       </c>
       <c r="BO203" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP203" s="50">
         <v>390000</v>
       </c>
       <c r="BQ203" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="204" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A204" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B204" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D204" s="55">
         <v>39</v>
       </c>
       <c r="E204" s="55" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F204" s="55" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G204" s="43">
         <v>66729</v>
@@ -44576,24 +44579,24 @@
         <v>14.046892341842398</v>
       </c>
       <c r="BO204" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP204" s="50">
         <v>600000</v>
       </c>
       <c r="BQ204" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="205" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A205" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B205" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D205" s="55">
         <v>52</v>
@@ -44785,24 +44788,24 @@
         <v>6.0975609756097562</v>
       </c>
       <c r="BO205" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP205" s="50">
         <v>250000</v>
       </c>
       <c r="BQ205" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="206" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A206" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B206" s="35" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D206" s="55">
         <v>41</v>
@@ -44994,30 +44997,30 @@
         <v>15.701614236130242</v>
       </c>
       <c r="BO206" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP206" s="50">
         <v>700000</v>
       </c>
       <c r="BQ206" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="207" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A207" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B207" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D207" s="55">
         <v>5</v>
       </c>
       <c r="E207" s="55" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F207" s="55">
         <v>15</v>
@@ -45203,24 +45206,24 @@
         <v>18.281535648994517</v>
       </c>
       <c r="BO207" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP207" s="50">
         <v>60000</v>
       </c>
       <c r="BQ207" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="208" spans="1:69" x14ac:dyDescent="0.3">
       <c r="A208" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B208" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C208" s="39" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D208" s="79">
         <v>9</v>
@@ -45412,11 +45415,11 @@
         <v>27.57352941176471</v>
       </c>
       <c r="BO208" s="50" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="BP208" s="50"/>
       <c r="BQ208" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="209" spans="1:69" x14ac:dyDescent="0.3">

--- a/24-25_KBL_stats.xlsx
+++ b/24-25_KBL_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\2026\KBL Stats Analyzer 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED7841B-582C-4B3A-AC15-39C24444263B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC76DB70-B406-4AE0-BD43-F075A3709D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="339">
   <si>
     <t>Season</t>
   </si>
@@ -1115,6 +1115,14 @@
   <si>
     <t>평균 FT 시도</t>
   </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2429,11 +2437,11 @@
         <v>10</v>
       </c>
       <c r="AA2" s="29">
-        <f t="shared" ref="AA2:AA13" si="8">Y2/$D2</f>
+        <f t="shared" ref="AA2:AA12" si="8">Y2/$D2</f>
         <v>0.13636363636363635</v>
       </c>
       <c r="AB2" s="29">
-        <f t="shared" ref="AB2:AB13" si="9">Z2/$D2</f>
+        <f t="shared" ref="AB2:AB12" si="9">Z2/$D2</f>
         <v>0.22727272727272727</v>
       </c>
       <c r="AC2" s="20">
@@ -4949,7 +4957,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="S12" s="20">
-        <f t="shared" ref="S11:S74" si="28">O12/P12</f>
+        <f t="shared" ref="S12:S74" si="28">O12/P12</f>
         <v>0.5</v>
       </c>
       <c r="T12" s="18">
@@ -4967,7 +4975,7 @@
         <v>3.1428571428571428</v>
       </c>
       <c r="X12" s="20">
-        <f t="shared" ref="X11:X74" si="29">T12/U12</f>
+        <f t="shared" ref="X12:X74" si="29">T12/U12</f>
         <v>0.38636363636363635</v>
       </c>
       <c r="Y12" s="18">
@@ -5192,11 +5200,11 @@
         <v>12</v>
       </c>
       <c r="L13" s="29">
-        <f t="shared" ref="L11:L66" si="30">J13/$D13</f>
+        <f t="shared" ref="L13:L66" si="30">J13/$D13</f>
         <v>0.18181818181818182</v>
       </c>
       <c r="M13" s="29">
-        <f t="shared" ref="M11:M66" si="31">K13/$D13</f>
+        <f t="shared" ref="M13:M66" si="31">K13/$D13</f>
         <v>1.0909090909090908</v>
       </c>
       <c r="N13" s="20">
@@ -5210,11 +5218,11 @@
         <v>3</v>
       </c>
       <c r="Q13" s="29">
-        <f t="shared" ref="Q11:Q74" si="32">O13/$D13</f>
+        <f t="shared" ref="Q13:Q74" si="32">O13/$D13</f>
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="R13" s="29">
-        <f t="shared" ref="R11:R74" si="33">P13/$D13</f>
+        <f t="shared" ref="R13:R74" si="33">P13/$D13</f>
         <v>0.27272727272727271</v>
       </c>
       <c r="S13" s="20">
@@ -5228,11 +5236,11 @@
         <v>9</v>
       </c>
       <c r="V13" s="29">
-        <f t="shared" ref="V11:V74" si="34">T13/$D13</f>
+        <f t="shared" ref="V13:V74" si="34">T13/$D13</f>
         <v>9.0909090909090912E-2</v>
       </c>
       <c r="W13" s="29">
-        <f t="shared" ref="W11:W74" si="35">U13/$D13</f>
+        <f t="shared" ref="W13:W74" si="35">U13/$D13</f>
         <v>0.81818181818181823</v>
       </c>
       <c r="X13" s="20">
@@ -5246,11 +5254,11 @@
         <v>6</v>
       </c>
       <c r="AA13" s="29">
-        <f t="shared" ref="AA11:AA74" si="36">Y13/$D13</f>
+        <f t="shared" ref="AA13:AA74" si="36">Y13/$D13</f>
         <v>0.27272727272727271</v>
       </c>
       <c r="AB13" s="29">
-        <f t="shared" ref="AB11:AB74" si="37">Z13/$D13</f>
+        <f t="shared" ref="AB13:AB74" si="37">Z13/$D13</f>
         <v>0.54545454545454541</v>
       </c>
       <c r="AC13" s="20">
@@ -21153,7 +21161,9 @@
       <c r="BP72" s="21">
         <v>48931</v>
       </c>
-      <c r="BQ72" s="13"/>
+      <c r="BQ72" s="13" t="s">
+        <v>337</v>
+      </c>
       <c r="BR72" s="38"/>
       <c r="BS72" s="40"/>
       <c r="BT72" s="40"/>
@@ -43292,7 +43302,9 @@
       <c r="BP155" s="21">
         <v>45000</v>
       </c>
-      <c r="BQ155" s="65"/>
+      <c r="BQ155" s="65" t="s">
+        <v>338</v>
+      </c>
       <c r="BR155" s="65"/>
       <c r="BS155" s="65"/>
       <c r="BT155" s="65"/>

--- a/24-25_KBL_stats.xlsx
+++ b/24-25_KBL_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\2026\KBL Stats Analyzer 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC76DB70-B406-4AE0-BD43-F075A3709D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7804D037-FE56-439E-A929-5C70B735BF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{C857A6F3-DAC3-47BF-9FFB-2634F9EBE6C3}"/>
   </bookViews>
@@ -1137,7 +1137,7 @@
     <numFmt numFmtId="180" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
     <numFmt numFmtId="181" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1226,6 +1226,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -1485,7 +1491,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1692,6 +1698,12 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -11301,13 +11313,13 @@
       <c r="BQ35" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR35" s="38">
+      <c r="BR35" s="69">
         <v>358.3</v>
       </c>
-      <c r="BS35" s="40">
+      <c r="BS35" s="69">
         <v>470.4</v>
       </c>
-      <c r="BT35" s="40">
+      <c r="BT35" s="69">
         <v>112.1</v>
       </c>
       <c r="BU35" s="38">
@@ -11570,13 +11582,13 @@
       <c r="BQ36" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR36" s="38">
+      <c r="BR36" s="69">
         <v>646.36</v>
       </c>
-      <c r="BS36" s="40">
+      <c r="BS36" s="69">
         <v>982.96</v>
       </c>
-      <c r="BT36" s="40">
+      <c r="BT36" s="69">
         <v>336.6</v>
       </c>
       <c r="BU36" s="38">
@@ -11839,13 +11851,13 @@
       <c r="BQ37" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="BR37" s="38">
+      <c r="BR37" s="70">
         <v>50.35</v>
       </c>
-      <c r="BS37" s="40">
+      <c r="BS37" s="70">
         <v>63.35</v>
       </c>
-      <c r="BT37" s="40">
+      <c r="BT37" s="70">
         <v>13</v>
       </c>
       <c r="BU37" s="38">
@@ -12108,9 +12120,9 @@
       <c r="BQ38" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="BR38" s="67"/>
-      <c r="BS38" s="67"/>
-      <c r="BT38" s="67"/>
+      <c r="BR38" s="69"/>
+      <c r="BS38" s="69"/>
+      <c r="BT38" s="69"/>
       <c r="BU38" s="21"/>
       <c r="BV38" s="21"/>
       <c r="BW38" s="21"/>
@@ -12353,13 +12365,13 @@
       <c r="BQ39" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="BR39" s="38">
+      <c r="BR39" s="70">
         <v>29.99</v>
       </c>
-      <c r="BS39" s="40">
+      <c r="BS39" s="70">
         <v>37.49</v>
       </c>
-      <c r="BT39" s="40">
+      <c r="BT39" s="70">
         <v>7.5</v>
       </c>
       <c r="BU39" s="38">
@@ -12622,13 +12634,13 @@
       <c r="BQ40" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR40" s="38">
+      <c r="BR40" s="69">
         <v>302.82</v>
       </c>
-      <c r="BS40" s="40">
+      <c r="BS40" s="69">
         <v>382.62</v>
       </c>
-      <c r="BT40" s="40">
+      <c r="BT40" s="69">
         <v>79.8</v>
       </c>
       <c r="BU40" s="38">
@@ -12891,13 +12903,13 @@
       <c r="BQ41" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR41" s="38">
+      <c r="BR41" s="70">
         <v>1318.44</v>
       </c>
-      <c r="BS41" s="40">
+      <c r="BS41" s="70">
         <v>1788.84</v>
       </c>
-      <c r="BT41" s="40">
+      <c r="BT41" s="70">
         <v>470.4</v>
       </c>
       <c r="BU41" s="38">
@@ -13160,13 +13172,13 @@
       <c r="BQ42" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR42" s="38">
+      <c r="BR42" s="70">
         <v>12.11</v>
       </c>
-      <c r="BS42" s="40">
+      <c r="BS42" s="70">
         <v>28.21</v>
       </c>
-      <c r="BT42" s="40">
+      <c r="BT42" s="70">
         <v>16.100000000000001</v>
       </c>
       <c r="BU42" s="38">
@@ -13427,13 +13439,13 @@
       <c r="BQ43" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR43" s="38">
+      <c r="BR43" s="70">
         <v>701.57</v>
       </c>
-      <c r="BS43" s="40">
+      <c r="BS43" s="70">
         <v>979.37</v>
       </c>
-      <c r="BT43" s="40">
+      <c r="BT43" s="70">
         <v>277.8</v>
       </c>
       <c r="BU43" s="38">
@@ -13696,13 +13708,13 @@
       <c r="BQ44" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR44" s="38">
+      <c r="BR44" s="69">
         <v>201.96</v>
       </c>
-      <c r="BS44" s="40">
+      <c r="BS44" s="69">
         <v>286.06</v>
       </c>
-      <c r="BT44" s="40">
+      <c r="BT44" s="69">
         <v>84.1</v>
       </c>
       <c r="BU44" s="38">
@@ -13965,13 +13977,13 @@
       <c r="BQ45" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR45" s="38">
+      <c r="BR45" s="69">
         <v>7.78</v>
       </c>
-      <c r="BS45" s="40">
+      <c r="BS45" s="69">
         <v>10.88</v>
       </c>
-      <c r="BT45" s="40">
+      <c r="BT45" s="69">
         <v>3.1</v>
       </c>
       <c r="BU45" s="38">
@@ -14234,13 +14246,13 @@
       <c r="BQ46" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR46" s="38">
+      <c r="BR46" s="70">
         <v>1400.71</v>
       </c>
-      <c r="BS46" s="40">
+      <c r="BS46" s="70">
         <v>1919.51</v>
       </c>
-      <c r="BT46" s="40">
+      <c r="BT46" s="70">
         <v>518.79999999999995</v>
       </c>
       <c r="BU46" s="38">
@@ -14503,13 +14515,13 @@
       <c r="BQ47" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR47" s="38">
+      <c r="BR47" s="69">
         <v>141.22</v>
       </c>
-      <c r="BS47" s="40">
+      <c r="BS47" s="69">
         <v>195.22</v>
       </c>
-      <c r="BT47" s="40">
+      <c r="BT47" s="69">
         <v>54</v>
       </c>
       <c r="BU47" s="38">
@@ -14770,13 +14782,13 @@
       <c r="BQ48" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR48" s="38">
+      <c r="BR48" s="69">
         <v>54.82</v>
       </c>
-      <c r="BS48" s="40">
+      <c r="BS48" s="69">
         <v>86.92</v>
       </c>
-      <c r="BT48" s="40">
+      <c r="BT48" s="69">
         <v>32.1</v>
       </c>
       <c r="BU48" s="38">
@@ -15037,13 +15049,13 @@
       <c r="BQ49" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="BR49" s="38">
+      <c r="BR49" s="70">
         <v>901.6</v>
       </c>
-      <c r="BS49" s="40">
+      <c r="BS49" s="70">
         <v>1139.9000000000001</v>
       </c>
-      <c r="BT49" s="40">
+      <c r="BT49" s="70">
         <v>238.3</v>
       </c>
       <c r="BU49" s="38">
@@ -15306,9 +15318,9 @@
       <c r="BQ50" s="65" t="s">
         <v>275</v>
       </c>
-      <c r="BR50" s="38"/>
-      <c r="BS50" s="40"/>
-      <c r="BT50" s="40"/>
+      <c r="BR50" s="70"/>
+      <c r="BS50" s="70"/>
+      <c r="BT50" s="70"/>
       <c r="BU50" s="38"/>
       <c r="BV50" s="38"/>
       <c r="BW50" s="38"/>
@@ -15549,13 +15561,13 @@
       <c r="BQ51" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR51" s="38">
+      <c r="BR51" s="70">
         <v>0.38</v>
       </c>
-      <c r="BS51" s="40">
+      <c r="BS51" s="70">
         <v>4.9800000000000004</v>
       </c>
-      <c r="BT51" s="40">
+      <c r="BT51" s="70">
         <v>4.5999999999999996</v>
       </c>
       <c r="BU51" s="38">
@@ -15816,13 +15828,13 @@
       <c r="BQ52" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR52" s="38">
+      <c r="BR52" s="69">
         <v>238.71</v>
       </c>
-      <c r="BS52" s="67">
+      <c r="BS52" s="69">
         <v>330.11</v>
       </c>
-      <c r="BT52" s="67">
+      <c r="BT52" s="69">
         <v>91.4</v>
       </c>
       <c r="BU52" s="38">
@@ -16083,13 +16095,13 @@
       <c r="BQ53" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR53" s="38">
+      <c r="BR53" s="70">
         <v>852.72</v>
       </c>
-      <c r="BS53" s="40">
+      <c r="BS53" s="70">
         <v>1142.1199999999999</v>
       </c>
-      <c r="BT53" s="40">
+      <c r="BT53" s="70">
         <v>289.39999999999998</v>
       </c>
       <c r="BU53" s="38">
@@ -16350,13 +16362,13 @@
       <c r="BQ54" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR54" s="38">
+      <c r="BR54" s="70">
         <v>2.57</v>
       </c>
-      <c r="BS54" s="40">
+      <c r="BS54" s="70">
         <v>2.57</v>
       </c>
-      <c r="BT54" s="40">
+      <c r="BT54" s="70">
         <v>0</v>
       </c>
       <c r="BU54" s="38">
@@ -16619,13 +16631,13 @@
       <c r="BQ55" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR55" s="38">
+      <c r="BR55" s="69">
         <v>172.86</v>
       </c>
-      <c r="BS55" s="40">
+      <c r="BS55" s="69">
         <v>222.86</v>
       </c>
-      <c r="BT55" s="40">
+      <c r="BT55" s="69">
         <v>50</v>
       </c>
       <c r="BU55" s="38">
@@ -16888,13 +16900,13 @@
       <c r="BQ56" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR56" s="38">
+      <c r="BR56" s="69">
         <v>415.65</v>
       </c>
-      <c r="BS56" s="40">
+      <c r="BS56" s="69">
         <v>543.45000000000005</v>
       </c>
-      <c r="BT56" s="40">
+      <c r="BT56" s="69">
         <v>127.8</v>
       </c>
       <c r="BU56" s="38">
@@ -17155,13 +17167,13 @@
       <c r="BQ57" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="BR57" s="38">
+      <c r="BR57" s="70">
         <v>229.24</v>
       </c>
-      <c r="BS57" s="40">
+      <c r="BS57" s="70">
         <v>353.84</v>
       </c>
-      <c r="BT57" s="40">
+      <c r="BT57" s="70">
         <v>124.6</v>
       </c>
       <c r="BU57" s="38">
@@ -17424,9 +17436,15 @@
       <c r="BQ58" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR58" s="38"/>
-      <c r="BS58" s="40"/>
-      <c r="BT58" s="40"/>
+      <c r="BR58" s="69">
+        <v>404.87</v>
+      </c>
+      <c r="BS58" s="69">
+        <v>510.07</v>
+      </c>
+      <c r="BT58" s="69">
+        <v>105.2</v>
+      </c>
       <c r="BU58" s="38"/>
       <c r="BV58" s="38"/>
       <c r="BW58" s="38"/>
@@ -17667,13 +17685,13 @@
       <c r="BQ59" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="BR59" s="38">
+      <c r="BR59" s="69">
         <v>404.87</v>
       </c>
-      <c r="BS59" s="40">
+      <c r="BS59" s="69">
         <v>510.07</v>
       </c>
-      <c r="BT59" s="40">
+      <c r="BT59" s="69">
         <v>105.2</v>
       </c>
       <c r="BU59" s="38">
@@ -17936,13 +17954,13 @@
       <c r="BQ60" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR60" s="38">
+      <c r="BR60" s="70">
         <v>104.91</v>
       </c>
-      <c r="BS60" s="40">
+      <c r="BS60" s="70">
         <v>139.51</v>
       </c>
-      <c r="BT60" s="40">
+      <c r="BT60" s="70">
         <v>34.6</v>
       </c>
       <c r="BU60" s="38">
@@ -18205,13 +18223,13 @@
       <c r="BQ61" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR61" s="38">
+      <c r="BR61" s="69">
         <v>3.62</v>
       </c>
-      <c r="BS61" s="40">
+      <c r="BS61" s="69">
         <v>8.02</v>
       </c>
-      <c r="BT61" s="40">
+      <c r="BT61" s="69">
         <v>4.4000000000000004</v>
       </c>
       <c r="BU61" s="38">
@@ -18474,13 +18492,13 @@
       <c r="BQ62" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR62" s="38">
+      <c r="BR62" s="69">
         <v>105.68</v>
       </c>
-      <c r="BS62" s="40">
+      <c r="BS62" s="69">
         <v>137.47999999999999</v>
       </c>
-      <c r="BT62" s="40">
+      <c r="BT62" s="69">
         <v>31.8</v>
       </c>
       <c r="BU62" s="38">
@@ -18743,13 +18761,13 @@
       <c r="BQ63" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR63" s="38">
+      <c r="BR63" s="69">
         <v>453.39</v>
       </c>
-      <c r="BS63" s="40">
+      <c r="BS63" s="69">
         <v>595.59</v>
       </c>
-      <c r="BT63" s="40">
+      <c r="BT63" s="69">
         <v>142.19999999999999</v>
       </c>
       <c r="BU63" s="38">
@@ -19012,13 +19030,13 @@
       <c r="BQ64" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR64" s="38">
+      <c r="BR64" s="69">
         <v>1108.33</v>
       </c>
-      <c r="BS64" s="40">
+      <c r="BS64" s="69">
         <v>1481.43</v>
       </c>
-      <c r="BT64" s="40">
+      <c r="BT64" s="69">
         <v>373.1</v>
       </c>
       <c r="BU64" s="38">
@@ -19281,13 +19299,13 @@
       <c r="BQ65" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR65" s="38">
+      <c r="BR65" s="69">
         <v>127.27</v>
       </c>
-      <c r="BS65" s="40">
+      <c r="BS65" s="69">
         <v>176.67</v>
       </c>
-      <c r="BT65" s="40">
+      <c r="BT65" s="69">
         <v>49.4</v>
       </c>
       <c r="BU65" s="38">
@@ -19550,13 +19568,13 @@
       <c r="BQ66" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR66" s="38">
+      <c r="BR66" s="69">
         <v>12.7</v>
       </c>
-      <c r="BS66" s="40">
+      <c r="BS66" s="69">
         <v>19.8</v>
       </c>
-      <c r="BT66" s="40">
+      <c r="BT66" s="69">
         <v>7.1</v>
       </c>
       <c r="BU66" s="38">
@@ -19819,13 +19837,13 @@
       <c r="BQ67" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR67" s="38">
+      <c r="BR67" s="69">
         <v>857</v>
       </c>
-      <c r="BS67" s="40">
+      <c r="BS67" s="69">
         <v>1127.8</v>
       </c>
-      <c r="BT67" s="40">
+      <c r="BT67" s="69">
         <v>270.8</v>
       </c>
       <c r="BU67" s="38">
@@ -20088,13 +20106,13 @@
       <c r="BQ68" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR68" s="38">
+      <c r="BR68" s="70">
         <v>381.23</v>
       </c>
-      <c r="BS68" s="40">
+      <c r="BS68" s="70">
         <v>520.73</v>
       </c>
-      <c r="BT68" s="40">
+      <c r="BT68" s="70">
         <v>139.5</v>
       </c>
       <c r="BU68" s="38">
@@ -20357,13 +20375,13 @@
       <c r="BQ69" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR69" s="38">
+      <c r="BR69" s="70">
         <v>4.18</v>
       </c>
-      <c r="BS69" s="40">
+      <c r="BS69" s="70">
         <v>4.18</v>
       </c>
-      <c r="BT69" s="40">
+      <c r="BT69" s="70">
         <v>0</v>
       </c>
       <c r="BU69" s="38">
@@ -20626,13 +20644,13 @@
       <c r="BQ70" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR70" s="38">
+      <c r="BR70" s="69">
         <v>576.59</v>
       </c>
-      <c r="BS70" s="40">
+      <c r="BS70" s="69">
         <v>750.49</v>
       </c>
-      <c r="BT70" s="40">
+      <c r="BT70" s="69">
         <v>173.9</v>
       </c>
       <c r="BU70" s="38">
@@ -20895,13 +20913,13 @@
       <c r="BQ71" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="BR71" s="38">
+      <c r="BR71" s="70">
         <v>426.97</v>
       </c>
-      <c r="BS71" s="40">
+      <c r="BS71" s="70">
         <v>622.27</v>
       </c>
-      <c r="BT71" s="40">
+      <c r="BT71" s="70">
         <v>195.3</v>
       </c>
       <c r="BU71" s="38">
@@ -21164,9 +21182,9 @@
       <c r="BQ72" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="BR72" s="38"/>
-      <c r="BS72" s="40"/>
-      <c r="BT72" s="40"/>
+      <c r="BR72" s="69"/>
+      <c r="BS72" s="69"/>
+      <c r="BT72" s="69"/>
       <c r="BU72" s="38"/>
       <c r="BV72" s="38"/>
       <c r="BW72" s="38"/>
@@ -21409,13 +21427,13 @@
       <c r="BQ73" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR73" s="38">
+      <c r="BR73" s="69">
         <v>525.17999999999995</v>
       </c>
-      <c r="BS73" s="40">
+      <c r="BS73" s="69">
         <v>664.78</v>
       </c>
-      <c r="BT73" s="40">
+      <c r="BT73" s="69">
         <v>139.6</v>
       </c>
       <c r="BU73" s="38">
@@ -21678,13 +21696,13 @@
       <c r="BQ74" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="BR74" s="38">
+      <c r="BR74" s="69">
         <v>803.31</v>
       </c>
-      <c r="BS74" s="40">
+      <c r="BS74" s="69">
         <v>1177.51</v>
       </c>
-      <c r="BT74" s="40">
+      <c r="BT74" s="69">
         <v>374.2</v>
       </c>
       <c r="BU74" s="38">
